--- a/Data/data-lake/UWA/index_march_2025.xlsx
+++ b/Data/data-lake/UWA/index_march_2025.xlsx
@@ -1,132 +1,197 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Cloud/github/lake-richmond/Data/data-lake/UWA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthipsey/Local/Richmond/lake-richmond/Data/data-lake/UWA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9097B156-BFAA-2A41-8B27-FF101C0B2B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DAAB44-BADA-0D4F-8250-E71ED200F1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14100" yWindow="6240" windowWidth="27240" windowHeight="16440" xr2:uid="{BAA33D2D-9E55-2F48-B295-63C5DC3C4760}"/>
+    <workbookView xWindow="8940" yWindow="1300" windowWidth="51200" windowHeight="27000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
+  <si>
+    <t>Campaign</t>
+  </si>
+  <si>
+    <t>Site ID</t>
+  </si>
+  <si>
+    <t>Lat</t>
+  </si>
+  <si>
+    <t>Long</t>
+  </si>
+  <si>
+    <t>Bottom Depth</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>0a</t>
+  </si>
+  <si>
+    <t>SITE0c - AAQ177-CAD_0136_19800104_203809_0001.csv</t>
+  </si>
+  <si>
+    <t>0b</t>
+  </si>
   <si>
     <t>0c</t>
   </si>
   <si>
+    <t>SITE1 - AAQ177-CAD_0136_19800104_203448_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE2 - AAQ177-CAD_0136_19800104_205012_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE3 - AAQ177-CAD_0136_19800104_205402_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE4 - AAQ177-CAD_0136_19800104_205739_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE5 - AAQ177-CAD_0136_19800104_210155_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE6 - AAQ177-CAD_0136_19800104_210703_0001.csv</t>
+  </si>
+  <si>
     <t>7a</t>
   </si>
   <si>
+    <t>SITE7a - AAQ177-CAD_0136_19800104_211124_0001.csv</t>
+  </si>
+  <si>
     <t>7b</t>
   </si>
   <si>
+    <t>SITE7b - AAQ177-CAD_0136_19800104_212020_0001.csv</t>
+  </si>
+  <si>
     <t>8a</t>
   </si>
   <si>
+    <t>SITE8a - AAQ177-CAD_0136_19800104_211818_0001.csv</t>
+  </si>
+  <si>
     <t>8b</t>
   </si>
   <si>
-    <t>Site ID</t>
-  </si>
-  <si>
-    <t>Lat</t>
-  </si>
-  <si>
-    <t>Long</t>
-  </si>
-  <si>
-    <t>Campaign</t>
-  </si>
-  <si>
-    <t>Bottom Depth</t>
-  </si>
-  <si>
-    <t>Filename</t>
-  </si>
-  <si>
-    <t>SITE0c - AAQ177-CAD_0136_19800104_203809_0001.csv</t>
-  </si>
-  <si>
-    <t>SITE1 - AAQ177-CAD_0136_19800104_203448_0001.csv</t>
-  </si>
-  <si>
-    <t>SITE2 - AAQ177-CAD_0136_19800104_205012_0001.csv</t>
-  </si>
-  <si>
-    <t>SITE3 - AAQ177-CAD_0136_19800104_205402_0001.csv</t>
-  </si>
-  <si>
-    <t>SITE4 - AAQ177-CAD_0136_19800104_205739_0001.csv</t>
-  </si>
-  <si>
-    <t>SITE5 - AAQ177-CAD_0136_19800104_210155_0001.csv</t>
-  </si>
-  <si>
-    <t>SITE6 - AAQ177-CAD_0136_19800104_210703_0001.csv</t>
-  </si>
-  <si>
-    <t>SITE7a - AAQ177-CAD_0136_19800104_211124_0001.csv</t>
-  </si>
-  <si>
-    <t>SITE7b - AAQ177-CAD_0136_19800104_212020_0001.csv</t>
-  </si>
-  <si>
-    <t>SITE8a - AAQ177-CAD_0136_19800104_211818_0001.csv</t>
-  </si>
-  <si>
     <t>SITE8b - AAQ177-CAD_0136_19800104_211519_0001.csv</t>
   </si>
   <si>
-    <t>0a</t>
-  </si>
-  <si>
-    <t>0b</t>
-  </si>
-  <si>
     <t>10a</t>
   </si>
   <si>
     <t>10b</t>
+  </si>
+  <si>
+    <t>SITE1 - AAQ177-CAD_0136_19800221_210519_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE2 - AAQ177-CAD_0136_19800221_210909_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE3 - AAQ177-CAD_0136_19800221_211625_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE4 - AAQ177-CAD_0136_19800221_212023_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE5 - AAQ177-CAD_0136_19800221_212404_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE6 - AAQ177-CAD_0136_19800221_212843_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE7 - AAQ177-CAD_0136_19800221_213230_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE8 - AAQ177-CAD_0136_19800221_213707_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE1 - AAQ177-CAD_0136_20250817_140514_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE2 - AAQ177-CAD_0136_20250817_140938_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE3 - AAQ177-CAD_0136_20250817_141312_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE4 - AAQ177-CAD_0136_20250817_141743_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE5 - AAQ177-CAD_0136_20250817_142139_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE6 - AAQ177-CAD_0136_20250817_142540_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE7 - AAQ177-CAD_0136_20250817_143122_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE8 - AAQ177-CAD_0136_20250817_143554_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE1 - AAQ177-CAD_0136_20251018_152721_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE2 - AAQ177-CAD_0136_20251018_153201_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE3 - AAQ177-CAD_0136_20251018_153621_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE4 - AAQ177-CAD_0136_20251018_154008_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE5 - AAQ177-CAD_0136_20251018_154416_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE6 - AAQ177-CAD_0136_20251018_154918_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE7 - AAQ177-CAD_0136_20251018_155356_0001.csv</t>
+  </si>
+  <si>
+    <t>SITE8 - AAQ177-CAD_0136_20251018_155737_0001.csv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -137,7 +202,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -145,22 +210,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -183,44 +269,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -247,32 +333,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -299,24 +367,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -328,241 +378,246 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3120AAEF-2A03-C043-8B7A-6B835F73AB7A}">
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="48.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" style="4"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
         <v>-32.282238999999997</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2">
         <v>115.712091</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2">
         <v>0.1</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
         <v>-32.282483999999997</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3">
         <v>115.71246499999999</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>0</v>
+        <v>45738</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="C4">
         <v>-32.282899999999998</v>
@@ -574,163 +629,163 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B5" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B5" s="4">
         <v>1</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>-32.282967999999997</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5">
         <v>115.712808</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5">
         <v>7.8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B6" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B6" s="4">
         <v>2</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>-32.283999000000001</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6">
         <v>115.71316400000001</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>9.9</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B7" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B7" s="4">
         <v>3</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7">
         <v>-32.284976</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7">
         <v>115.713632</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7">
         <v>11.2</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B8" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B8" s="4">
         <v>4</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8">
         <v>-32.285508</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8">
         <v>115.714326</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8">
         <v>11.8</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B9" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B9" s="4">
         <v>5</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9">
         <v>-32.286437999999997</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9">
         <v>115.71494300000001</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9">
         <v>11.99</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B10" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B10" s="4">
         <v>6</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10">
         <v>-32.287205</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10">
         <v>115.71599500000001</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10">
         <v>12.7</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
         <v>-32.287931</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11">
         <v>115.71683299999999</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11">
         <v>12.36</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12">
         <v>-32.288345</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12">
         <v>115.71696900000001</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12">
         <v>8.1</v>
       </c>
       <c r="F12" t="s">
@@ -739,85 +794,805 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13">
         <v>-32.288539999999998</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13">
         <v>115.71747000000001</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13">
         <v>2.9</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14">
         <v>-32.288707000000002</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14">
         <v>115.71772</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14">
         <v>2.4</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B15" s="1" t="s">
+        <v>45738</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15">
         <v>-32.289226999999997</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15">
         <v>115.718087</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>45717</v>
-      </c>
-      <c r="B16" s="1" t="s">
+        <v>45738</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16">
         <v>-32.289521999999998</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16">
         <v>115.71813</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16">
         <v>0.1</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>45786</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>-32.282238999999997</v>
+      </c>
+      <c r="D17">
+        <v>115.712091</v>
+      </c>
+      <c r="E17">
+        <v>0.1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>45786</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>-32.282483999999997</v>
+      </c>
+      <c r="D18">
+        <v>115.71246499999999</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>45786</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>-32.282967999999997</v>
+      </c>
+      <c r="D19">
+        <v>115.712808</v>
+      </c>
+      <c r="E19">
+        <v>7.8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>45786</v>
+      </c>
+      <c r="B20" s="4">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>-32.283999000000001</v>
+      </c>
+      <c r="D20">
+        <v>115.71316400000001</v>
+      </c>
+      <c r="E20">
+        <v>9.9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>45786</v>
+      </c>
+      <c r="B21" s="4">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>-32.284976</v>
+      </c>
+      <c r="D21">
+        <v>115.713632</v>
+      </c>
+      <c r="E21">
+        <v>11.2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>45786</v>
+      </c>
+      <c r="B22" s="4">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>-32.285508</v>
+      </c>
+      <c r="D22">
+        <v>115.714326</v>
+      </c>
+      <c r="E22">
+        <v>11.8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>45786</v>
+      </c>
+      <c r="B23" s="4">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>-32.286437999999997</v>
+      </c>
+      <c r="D23">
+        <v>115.71494300000001</v>
+      </c>
+      <c r="E23">
+        <v>11.99</v>
+      </c>
+      <c r="F23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>45786</v>
+      </c>
+      <c r="B24" s="4">
+        <v>6</v>
+      </c>
+      <c r="C24">
+        <v>-32.287205</v>
+      </c>
+      <c r="D24">
+        <v>115.71599500000001</v>
+      </c>
+      <c r="E24">
+        <v>12.7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>45786</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25">
+        <v>-32.287931</v>
+      </c>
+      <c r="D25">
+        <v>115.71683299999999</v>
+      </c>
+      <c r="E25">
+        <v>12.36</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>45786</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26">
+        <v>-32.288707000000002</v>
+      </c>
+      <c r="D26">
+        <v>115.71772</v>
+      </c>
+      <c r="E26">
+        <v>2.4</v>
+      </c>
+      <c r="F26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>45786</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27">
+        <v>-32.289226999999997</v>
+      </c>
+      <c r="D27">
+        <v>115.718087</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>45786</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28">
+        <v>-32.289521999999998</v>
+      </c>
+      <c r="D28">
+        <v>115.71813</v>
+      </c>
+      <c r="E28">
+        <v>0.1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>45886</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29">
+        <v>-32.282238999999997</v>
+      </c>
+      <c r="D29">
+        <v>115.712091</v>
+      </c>
+      <c r="E29">
+        <v>0.1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>45886</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30">
+        <v>-32.282483999999997</v>
+      </c>
+      <c r="D30">
+        <v>115.71246499999999</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>45886</v>
+      </c>
+      <c r="B31" s="4">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>-32.282899999999998</v>
+      </c>
+      <c r="D31">
+        <v>115.712506</v>
+      </c>
+      <c r="E31">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>45886</v>
+      </c>
+      <c r="B32" s="4">
+        <v>2</v>
+      </c>
+      <c r="C32">
+        <v>-32.283999000000001</v>
+      </c>
+      <c r="D32">
+        <v>115.71316400000001</v>
+      </c>
+      <c r="E32">
+        <v>9.9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>45886</v>
+      </c>
+      <c r="B33" s="4">
+        <v>3</v>
+      </c>
+      <c r="C33">
+        <v>-32.284976</v>
+      </c>
+      <c r="D33">
+        <v>115.713632</v>
+      </c>
+      <c r="E33">
+        <v>11.2</v>
+      </c>
+      <c r="F33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>45886</v>
+      </c>
+      <c r="B34" s="4">
+        <v>4</v>
+      </c>
+      <c r="C34">
+        <v>-32.285508</v>
+      </c>
+      <c r="D34">
+        <v>115.714326</v>
+      </c>
+      <c r="E34">
+        <v>11.8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>45886</v>
+      </c>
+      <c r="B35" s="4">
+        <v>5</v>
+      </c>
+      <c r="C35">
+        <v>-32.286437999999997</v>
+      </c>
+      <c r="D35">
+        <v>115.71494300000001</v>
+      </c>
+      <c r="E35">
+        <v>11.99</v>
+      </c>
+      <c r="F35" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>45886</v>
+      </c>
+      <c r="B36" s="4">
+        <v>6</v>
+      </c>
+      <c r="C36">
+        <v>-32.287205</v>
+      </c>
+      <c r="D36">
+        <v>115.71599500000001</v>
+      </c>
+      <c r="E36">
+        <v>12.7</v>
+      </c>
+      <c r="F36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>45886</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37">
+        <v>-32.287931</v>
+      </c>
+      <c r="D37">
+        <v>115.71683299999999</v>
+      </c>
+      <c r="E37">
+        <v>12.36</v>
+      </c>
+      <c r="F37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>45886</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38">
+        <v>-32.288707000000002</v>
+      </c>
+      <c r="D38">
+        <v>115.71772</v>
+      </c>
+      <c r="E38">
+        <v>2.4</v>
+      </c>
+      <c r="F38" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>45886</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39">
+        <v>-32.289226999999997</v>
+      </c>
+      <c r="D39">
+        <v>115.718087</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>45886</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40">
+        <v>-32.289521999999998</v>
+      </c>
+      <c r="D40">
+        <v>115.71813</v>
+      </c>
+      <c r="E40">
+        <v>0.1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>45948</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41">
+        <v>-32.282238999999997</v>
+      </c>
+      <c r="D41">
+        <v>115.712091</v>
+      </c>
+      <c r="E41">
+        <v>0.1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>45948</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42">
+        <v>-32.282483999999997</v>
+      </c>
+      <c r="D42">
+        <v>115.71246499999999</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="2">
+        <v>45948</v>
+      </c>
+      <c r="B43" s="4">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>-32.282967999999997</v>
+      </c>
+      <c r="D43">
+        <v>115.712808</v>
+      </c>
+      <c r="E43">
+        <v>7.8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>45948</v>
+      </c>
+      <c r="B44" s="4">
+        <v>2</v>
+      </c>
+      <c r="C44">
+        <v>-32.283999000000001</v>
+      </c>
+      <c r="D44">
+        <v>115.71316400000001</v>
+      </c>
+      <c r="E44">
+        <v>9.9</v>
+      </c>
+      <c r="F44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
+        <v>45948</v>
+      </c>
+      <c r="B45" s="4">
+        <v>3</v>
+      </c>
+      <c r="C45">
+        <v>-32.284976</v>
+      </c>
+      <c r="D45">
+        <v>115.713632</v>
+      </c>
+      <c r="E45">
+        <v>11.2</v>
+      </c>
+      <c r="F45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="2">
+        <v>45948</v>
+      </c>
+      <c r="B46" s="4">
+        <v>4</v>
+      </c>
+      <c r="C46">
+        <v>-32.285508</v>
+      </c>
+      <c r="D46">
+        <v>115.714326</v>
+      </c>
+      <c r="E46">
+        <v>11.8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>45948</v>
+      </c>
+      <c r="B47" s="4">
+        <v>5</v>
+      </c>
+      <c r="C47">
+        <v>-32.286437999999997</v>
+      </c>
+      <c r="D47">
+        <v>115.71494300000001</v>
+      </c>
+      <c r="E47">
+        <v>11.99</v>
+      </c>
+      <c r="F47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>45948</v>
+      </c>
+      <c r="B48" s="4">
+        <v>6</v>
+      </c>
+      <c r="C48">
+        <v>-32.287205</v>
+      </c>
+      <c r="D48">
+        <v>115.71599500000001</v>
+      </c>
+      <c r="E48">
+        <v>12.7</v>
+      </c>
+      <c r="F48" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>45948</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49">
+        <v>-32.288345</v>
+      </c>
+      <c r="D49">
+        <v>115.71696900000001</v>
+      </c>
+      <c r="E49">
+        <v>8.1</v>
+      </c>
+      <c r="F49" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>45948</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50">
+        <v>-32.288707000000002</v>
+      </c>
+      <c r="D50">
+        <v>115.71772</v>
+      </c>
+      <c r="E50">
+        <v>2.4</v>
+      </c>
+      <c r="F50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>45948</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51">
+        <v>-32.289226999999997</v>
+      </c>
+      <c r="D51">
+        <v>115.718087</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>45948</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52">
+        <v>-32.289521999999998</v>
+      </c>
+      <c r="D52">
+        <v>115.71813</v>
+      </c>
+      <c r="E52">
+        <v>0.1</v>
+      </c>
+      <c r="F52" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>